--- a/AAII_Financials/Yearly/LNWO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LNWO_YR_FIN.xlsx
@@ -2704,13 +2704,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>259000</v>
+        <v>179000</v>
       </c>
       <c r="E83" s="3">
-        <v>212000</v>
+        <v>134000</v>
       </c>
       <c r="F83" s="3">
-        <v>185000</v>
+        <v>117000</v>
       </c>
       <c r="G83" s="3">
         <v>111000</v>
